--- a/04_DESIGN_TABLES/DesignTable_2403.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2403.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA40"/>
+  <dimension ref="A1:AB40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -607,6 +607,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3291,7 +3296,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
@@ -3301,12 +3306,17 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>unequal bores - bore step location unsourced | DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>unequal bores - bore step location unsourced | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p005-t01: agrees on L1@DRIVE, HEXB@HEX, D1@BORE, D2@BORE</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2403-20-16</t>
         </is>
       </c>
     </row>
@@ -3917,24 +3927,88 @@
           <t>2403-04-02</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="P36" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>37</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.062</v>
+      </c>
       <c r="T36" t="inlineStr">
         <is>
           <t>2403-04-02</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>7/16-20</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>5/16-24</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1@DRIVE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-04-02 col "L LGTH" = "1.270" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 200.4, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; HEXB@HEX: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-04-02 col "C HEX" = "0.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 200.4, page verified) [Brennan = yes 2026-10-18] - body hex across flats; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; D1@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-04-02 col "B1 DRILL" = "0.172" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 200.4, page verified) [Brennan = yes 2026-10-18] - bore at end A (first dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 30/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (3 differ, e.g. 2403-06-05 0.3 vs 0.234); D2@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-04-02 col "B2 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 200.4, page verified) [Brennan = yes 2026-10-18] - bore at end B (second dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 32/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2403-03-03 0.13 vs 1.25); THDMAJ_A@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B1 7/16-20; THDMAJ_B@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B2 5/16-24; JICA_RELIEFL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICA_THDZ@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICA_CONEDIA@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICA_LANDL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICA_SEATL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); JICB_RELIEFL@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICB_THDZ@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICB_CONEDIA@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICB_LANDL@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICB_SEATL@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; $PRP@EndA_Thread: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text (format of the built 2403 rows); $PRP@EndB_Thread: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L1 / hex / D1 / D2 from the Brennan TFA catalog p5 alone (no OMi dimension, no Air-Way row); JIC ends from the end library</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -3945,6 +4019,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2403-04-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3991,24 +4070,88 @@
           <t>2403-10-04</t>
         </is>
       </c>
+      <c r="B38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="P38" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>37</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.172</v>
+      </c>
       <c r="T38" t="inlineStr">
         <is>
           <t>2403-10-04</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>7/8-14</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>7/16-20</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1@DRIVE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-10-04 col "L LGTH" = "1.67" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 321.4, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; HEXB@HEX: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-10-04 col "C HEX" = "0.937" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 321.4, page verified) [Brennan = yes 2026-10-18] - body hex across flats; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; D1@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-10-04 col "B1 DRILL" = "0.484" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 321.4, page verified) [Brennan = yes 2026-10-18] - bore at end A (first dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 30/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (3 differ, e.g. 2403-06-05 0.3 vs 0.234); D2@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-10-04 col "B2 DRILL" = "0.172" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 321.4, page verified) [Brennan = yes 2026-10-18] - bore at end B (second dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 32/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2403-03-03 0.13 vs 1.25); THDMAJ_A@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B1 7/8-14; THDMAJ_B@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B2 7/16-20; JICA_RELIEFL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICA_THDZ@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICA_CONEDIA@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICA_LANDL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICA_SEATL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); JICB_RELIEFL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICB_THDZ@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICB_CONEDIA@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICB_LANDL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICB_SEATL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; $PRP@EndA_Thread: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text (format of the built 2403 rows); $PRP@EndB_Thread: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L1 / hex / D1 / D2 from the Brennan TFA catalog p5 alone (no OMi dimension, no Air-Way row); JIC ends from the end library</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -4019,6 +4162,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2403-10-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -4028,24 +4176,88 @@
           <t>2403-16-10</t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="P39" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>37</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.484</v>
+      </c>
       <c r="T39" t="inlineStr">
         <is>
           <t>2403-16-10</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>7/8-14</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1@DRIVE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-16-10 col "L LGTH" = "2.10" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 472.6, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; HEXB@HEX: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-16-10 col "C HEX" = "1.375" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 472.6, page verified) [Brennan = yes 2026-10-18] - body hex across flats; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; D1@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-16-10 col "B1 DRILL" = "0.844" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 472.6, page verified) [Brennan = yes 2026-10-18] - bore at end A (first dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 30/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (3 differ, e.g. 2403-06-05 0.3 vs 0.234); D2@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-16-10 col "B2 DRILL" = "0.484" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 472.6, page verified) [Brennan = yes 2026-10-18] - bore at end B (second dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 32/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2403-03-03 0.13 vs 1.25); THDMAJ_A@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B1 1 5/16-12; THDMAJ_B@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B2 7/8-14; JICA_RELIEFL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICA_THDZ@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICA_CONEDIA@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICA_LANDL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICA_SEATL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); JICB_RELIEFL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICB_THDZ@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICB_CONEDIA@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICB_LANDL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICB_SEATL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; $PRP@EndA_Thread: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text (format of the built 2403 rows); $PRP@EndB_Thread: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L1 / hex / D1 / D2 from the Brennan TFA catalog p5 alone (no OMi dimension, no Air-Way row); JIC ends from the end library</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4056,6 +4268,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2403-16-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -4065,24 +4282,88 @@
           <t>2403-24-16</t>
         </is>
       </c>
+      <c r="B40" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="P40" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>37</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.844</v>
+      </c>
       <c r="T40" t="inlineStr">
         <is>
           <t>2403-24-16</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1 7/8-12</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1@DRIVE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-24-16 col "L LGTH" = "2.580" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 553.2, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; HEXB@HEX: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-24-16 col "C HEX" = "2.000" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 553.2, page verified) [Brennan = yes 2026-10-18] - body hex across flats; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; D1@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-24-16 col "B1 DRILL" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 553.2, page verified) [Brennan = yes 2026-10-18] - bore at end A (first dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 30/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (3 differ, e.g. 2403-06-05 0.3 vs 0.234); D2@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-24-16 col "B2 DRILL" = "0.844" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 553.2, page verified) [Brennan = yes 2026-10-18] - bore at end B (second dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 32/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2403-03-03 0.13 vs 1.25); THDMAJ_A@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B1 1-7/8-12; THDMAJ_B@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B2 1-5/16-12; JICA_RELIEFL@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICA_THDZ@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICA_CONEDIA@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICA_LANDL@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICA_SEATL@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); JICB_RELIEFL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICB_THDZ@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICB_CONEDIA@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICB_LANDL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICB_SEATL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; $PRP@EndA_Thread: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text (format of the built 2403 rows); $PRP@EndB_Thread: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L1 / hex / D1 / D2 from the Brennan TFA catalog p5 alone (no OMi dimension, no Air-Way row); JIC ends from the end library</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -4093,6 +4374,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2403-24-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
